--- a/output/xpath_generator/xpath_details.xlsx
+++ b/output/xpath_generator/xpath_details.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C45"/>
+  <dimension ref="A1:C17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,748 +448,272 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>XPath for input with ID = 'user-name':</t>
+          <t>### 1. XPath for the `input` element with `id='user-name'`:</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1. //input[@id='user-name']</t>
+          <t>1. `//input[@id='user-name']`</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Login Page Demo Url</t>
+          <t>sauce_domo_login_page</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>XPath for input with ID = 'password':</t>
+          <t>#### Based on `name`:</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>1. //input[@id='password']</t>
+          <t>3. `//input[@name='login-button']`</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Login Page Demo Url</t>
+          <t>sauce_domo_login_page</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>XPath for input with ID = 'login-button':</t>
+          <t>### 2. XPath for the `input` element with `id='password'`:</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>1. //input[@id='login-button']</t>
+          <t>1. `//input[@id='password']`</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Login Page Demo Url</t>
+          <t>sauce_domo_login_page</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>1. XPath expressions for the button with id 'react-burger-menu-btn':</t>
+          <t>```xpath</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>- //button[@id='react-burger-menu-btn']</t>
+          <t>//button[@id='remove-test.allthethings()-t-shirt-(red)']</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Product Page Demo Url</t>
+          <t>sauce_domo_product_page</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>5. XPath expressions for the button with id 'add-to-cart-sauce-labs-fleece-jacket':</t>
+          <t>```xpath</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>- //button[@id='add-to-cart-sauce-labs-fleece-jacket']</t>
+          <t xml:space="preserve">//button[@class='btn btn_secondary btn_small btn_inventory '] </t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Product Page Demo Url</t>
+          <t>sauce_domo_product_page</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>6. XPath expressions for the button with id 'add-to-cart-sauce-labs-onesie':</t>
+          <t>```xpath</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>- //button[@id='add-to-cart-sauce-labs-onesie']</t>
+          <t>//button[@name='remove-test.allthethings()-t-shirt-(red)']</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Product Page Demo Url</t>
+          <t>sauce_domo_product_page</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>7. XPath expressions for the button with id 'add-to-cart-test.allthethings()-t-shirt-(red)':</t>
+          <t>```xpath</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>- //button[@id='add-to-cart-test.allthethings()-t-shirt-(red)']</t>
+          <t>//button[text()='Remove']</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Product Page Demo Url</t>
+          <t>sauce_domo_product_page</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>XPath for PowerBI</t>
+          <t>```xpath</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t xml:space="preserve">    "description": "Text element with text '$0.4M'",</t>
+          <t>//button[contains(@id, 'test.allthethings()-t-shirt-(red)')]</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Powerbipage</t>
+          <t>sauce_domo_product_page</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>XPath for PowerBI</t>
+          <t>```xpath</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t xml:space="preserve">    "xpath": "//*[text()[contains(.,'$0.4M')]]"</t>
+          <t>//button[contains(text(), 'Remove') and @id='remove-test.allthethings()-t-shirt-(red)']</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Powerbipage</t>
+          <t>sauce_domo_product_page</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>XPath for PowerBI</t>
+          <t>```xpath</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t xml:space="preserve">    "description": "Text element with class 'label' and text '$0.04M'",</t>
+          <t>//button[@id='remove-test.allthethings()-t-shirt-(red)' and contains(@class, 'btn_inventory')]</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Powerbipage</t>
+          <t>sauce_domo_product_page</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>XPath for PowerBI</t>
+          <t>```</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t xml:space="preserve">    "xpath": "//*[contains(@class, 'label')]//*[contains(text(), '$0.04M')]"</t>
+          <t>//input[@id='login-button']</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Powerbipage</t>
+          <t>demo_login</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>XPath for PowerBI</t>
+          <t>```</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t xml:space="preserve">    "description": "Text element with text '$200M'",</t>
+          <t>//input[@id='user-name']</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Powerbipage</t>
+          <t>LOGIN_PAGE</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>XPath for PowerBI</t>
+          <t>```</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t xml:space="preserve">    "xpath": "//*[text()[contains(.,'$200M')]]"</t>
+          <t>//input[@name='user-name']</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Powerbipage</t>
+          <t>LOGIN_PAGE</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>XPath for PowerBI</t>
+          <t>```</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t xml:space="preserve">    "description": "Text element with class 'label' and text 'Planned Spend'",</t>
+          <t>//input[@id='password']</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Powerbipage</t>
+          <t>LOGIN_PAGE</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>XPath for PowerBI</t>
+          <t>```</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t xml:space="preserve">    "xpath": "//*[contains(@class, 'label')]//*[contains(text(), 'Planned Spend')]"</t>
+          <t>//input[@name='login-button']</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Powerbipage</t>
+          <t>LOGIN_PAGE</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>XPath for PowerBI</t>
+          <t>```</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t xml:space="preserve">    "description": "Text element with class 'value' and text '($14M)'",</t>
+          <t>//button[@name='add-to-cart-test.allthethings()-t-shirt-(red)']</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Powerbipage</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>XPath for PowerBI</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    "xpath": "//*[contains(@class, 'value')]//*[contains(text(), '($14M)')]"</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Powerbipage</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>XPath for input with id 'user-name':</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>1. `//input[@id='user-name']`</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Login page latest</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>XPath for input with id 'user-name':</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>1. `//input[@id='password']`</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Login page latest</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>For the Button with ID 'react-burger-menu-btn':</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>1. //button[@id='react-burger-menu-btn']</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Product page latest</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>For the Button with ID 'add-to-cart-sauce-labs-bike-light' and class 'btn btn_primary btn_small btn_inventory':</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>1. //button[@id='add-to-cart-sauce-labs-bike-light']</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Product page latest</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>For the Button with ID 'add-to-cart-test.allthethings()-t-shirt-(red)' and class 'btn btn_primary btn_small btn_inventory':</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>4. //button[contains(@id, 'add-to-cart-test.allthethings()-t-shirt-(red)')]</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Product page latest</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>For the Button with ID 'add-to-cart-test.allthethings()-t-shirt-(red)' and class 'btn btn_primary btn_small btn_inventory':</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>5. //button[text()='Add to cart']</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Product page latest</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>6. 'Checkout' button:</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>- //button[contains(text(), 'Checkout')]</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>cart page latest</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>XPath for button with id "login-button":</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>5. `//input[contains(@class, 'btn_action')]`</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>ne page</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>XPath expressions for the input tag with id 'password':</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>3. `//input[@class='input_error form_input']`</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>sxa</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>1. XPath expressions for the "user-name" input:</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>//input[@name='user-name']</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>asd</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Below are the XPath expressions for the above elements:</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>1. //button[@id='react-burger-menu-btn']</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>asdp</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>For Button with id='add-to-cart-test.allthethings()-t-shirt-(red)':</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>1. //button[@id='add-to-cart-test.allthethings()-t-shirt-(red)']</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>asdp</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>XPath for tag 'a' with class 'ns-y7o64-e-23' and text 'Learn More':</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>1. //a[@class='ns-y7o64-e-23' and text()='Learn More']</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>iframe</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Input Element - password:</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>5) //*[@id='password']</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>login page</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Input Element - password:</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>7) //*[contains(@id, 'password')]</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>login page</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Input Element - password:</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>6) //input[contains(@class, 'form_input')]</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>login page</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>1. XPath for the user name input field:</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   - `//input[@id='user-name']`</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Final_login_page</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>2. XPath for the password input field:</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   - `//input[@id='password']`</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Final_login_page</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>3. XPath for the login button input field:</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   - `//input[@id='login-button']`</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Final_login_page</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>1. XPath for button with id 'react-burger-menu-btn':</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   * //button[@id='react-burger-menu-btn']</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Final_product_page</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>3. XPath for button with id 'add-to-cart-sauce-labs-backpack':</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   * //button[@id='add-to-cart-sauce-labs-backpack']</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Final_product_page</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>4. XPath for button with id 'add-to-cart-sauce-labs-bike-light':</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   * //button[@id='add-to-cart-sauce-labs-bike-light']</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Final_product_page</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>4. XPath for button with id 'add-to-cart-sauce-labs-bike-light':</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   * //*[@name='add-to-cart-sauce-labs-bolt-t-shirt']</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Final_product_page</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>4. XPath for button with id 'add-to-cart-sauce-labs-bike-light':</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>6. XPath for button with id 'add-to-cart-sauce-labs-fleece-jacket':</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Final_product_page</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>4. XPath for button with id 'add-to-cart-sauce-labs-bike-light':</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   * //button[@id='add-to-cart-sauce-labs-fleece-jacket']</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Final_product_page</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>[</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    "xpath": "//*[name()='text']//*[contains(text(), '$0M')]"</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>power_final_page</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>XPath for input element with class 'submit-button btn_action' and name 'login-button':</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>15. //*[@class='submit-button btn_action' and @name='login-button']</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>my page</t>
+          <t>PRODUCT</t>
         </is>
       </c>
     </row>

--- a/output/xpath_generator/xpath_details.xlsx
+++ b/output/xpath_generator/xpath_details.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C17"/>
+  <dimension ref="A1:C20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -717,6 +717,57 @@
         </is>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>```</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>//button[@id='react-burger-menu-btn' and text()='Open Menu']</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>checkout page</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>```</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>//input[@id='postal-code']</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>checkout page</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>```</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>//input[@id='continue']</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>checkout page</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/xpath_generator/xpath_details.xlsx
+++ b/output/xpath_generator/xpath_details.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C20"/>
+  <dimension ref="A1:C23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -768,6 +768,57 @@
         </is>
       </c>
     </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>```</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>//button[@id='add-to-cart-sauce-labs-backpack' and text()='Add to cart']</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Adding_products</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>```</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>//button[@id='add-to-cart-sauce-labs-bolt-t-shirt' and text()='Add to cart']</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Adding_products</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>```</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>//button[@id='add-to-cart-sauce-labs-onesie' and text()='Add to cart']</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Adding_products</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/xpath_generator/xpath_details.xlsx
+++ b/output/xpath_generator/xpath_details.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C23"/>
+  <dimension ref="A1:C26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -819,6 +819,57 @@
         </is>
       </c>
     </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>```</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>//button[@id='react-burger-menu-btn']</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>remove_from_checkout</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>```</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>//button[@id='cancel' and text()='Cancel']</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>remove_from_checkout</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>```</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>//button[@id='finish' and @name='finish']</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>remove_from_checkout</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/xpath_generator/xpath_details.xlsx
+++ b/output/xpath_generator/xpath_details.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C30"/>
+  <dimension ref="A1:C82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -938,6 +938,890 @@
         </is>
       </c>
     </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Login Button</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">//form//input[@id='login-button']  </t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Login Button</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">//div[contains(@class, 'form-group')]//input[@id='login-button']  </t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Login Button</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">//*[@id='login-button']//parent::div  </t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Login Button</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>//*[@id='login-button']//preceding-sibling::*</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Login Button (input#login-button)  </t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>//*//input[@name='login-button']</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Login Button</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>//div[contains(@class, 'submit-button')]//input[@id='login-button']</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>user-name</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">//input[@name='user-name']  </t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>### Add to Cart: Test AllTheThings T-Shirt (Red) (button with id="add-to-cart-test.allthethings()-t-shirt-(red)")</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">//button[text()='Add to cart']  </t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>### Open Menu</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">//button[@id='react-burger-menu-btn']  </t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>tes</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Checkout</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">//button[contains(@class, 'btn_action')]  </t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>### Open Menu Button</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">//button[text()='Open Menu']  </t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>### Open Menu (button with id=react-burger-menu-btn)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">//button[@text()='Open Menu']  </t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Open Menu</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>//button[text()='Open Menu']</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>### Open Menu</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">//button[@id='react-burger-menu-btn']  </t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Login Button (input)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>//ancestor::form//input[@id='login-button']</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Login Button</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">//input[contains(@name, 'login-button')]  </t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Login Button</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">//input[parent::*[@class='form-actions']]  </t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>### Element: input[id='login-button']</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>//input[@id='login-button' and (@class='submit-button btn_action' or @name='login-button')]</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>User Name Input</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">//input[@id='user-name']  </t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>User Name Input Field (id=user-name)</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>/input[@id='user-name']</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>User Name Input Field:</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>//input[@id='user-name']</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>User-Name Input Field</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">//input[@id='user-name']  </t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>sauce_demo_login</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Password Input Field</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">//input[@id='password']  </t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>sauce_demo_login</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Login Button</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">//input[@id='login-button']  </t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>sauce_demo_login</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>### Element: Close button</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">//button[@class='close']  </t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Equfix_place_an_alert</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>### Element: CONTINUE button</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">//button[@id='continue-button']  </t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Equfix_place_an_alert</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>### Element: zip</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">//input[@id='zip']  </t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Equfix_place_an_alert</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>### Element: Select state</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">//button[contains(@text, 'Select state')]  </t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Equfix_place_an_alert</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>### Element: city</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">//input[@id='city']  </t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Equfix_place_an_alert</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>### Element: addressLine2Id</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">//input[@id='addressLine2Id']  </t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Equfix_place_an_alert</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>### Element: address</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">//input[@id='address']  </t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Equfix_place_an_alert</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>### Element: phoneNumber</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">//input[@id='phoneNumber']  </t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Equfix_place_an_alert</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>### Element: ssn</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">//input[@id='ssn']  </t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Equfix_place_an_alert</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>### Element: dob</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">//input[@id='dob']  </t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Equfix_place_an_alert</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>### Element: lastName</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">//input[@id='lastName']  </t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Equfix_place_an_alert</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>### Element: firstNameId</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">//input[@id='firstNameId']  </t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Equfix_place_an_alert</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>### firstNameId</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">//input[@id='firstNameId']  </t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Equfixplaceanalert</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>### lastName</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">//input[@id='lastName']  </t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Equfixplaceanalert</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>### dob</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">//input[@id='dob']  </t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Equfixplaceanalert</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>### ssn</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">//input[@id='ssn']  </t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Equfixplaceanalert</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>### phoneNumber</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">//input[@id='phoneNumber']  </t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Equfixplaceanalert</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>### address</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">//input[@id='address']  </t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Equfixplaceanalert</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>### addressLine2Id</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">//input[@id='addressLine2Id']  </t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Equfixplaceanalert</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>### city</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">//input[@id='city']  </t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Equfixplaceanalert</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>### zip</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">//input[@id='zip']  </t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Equfixplaceanalert</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>### efx-dropdown-label-796908</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">//button[starts-with(@id, 'efx-dropdown-label')]  </t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Equfixplaceanalert</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>### continue-button</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">//button[@id='continue-button']  </t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Equfixplaceanalert</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>User Name Input</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">//input[@id='user-name']  </t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Sauce_demo_login</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>User Name Input</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">//input[@name='user-name']  </t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Sauce_demo_login</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>User Name Input</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">//input[@id='user-name' and @name='user-name']  </t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Sauce_demo_login</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Password Input</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">//input[@id='password']  </t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Sauce_demo_login</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Login Button</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">//input[@id='login-button']  </t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Sauce_demo_login</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/xpath_generator/xpath_details.xlsx
+++ b/output/xpath_generator/xpath_details.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C82"/>
+  <dimension ref="A1:C85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1745,7 +1745,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t xml:space="preserve">//input[@id='user-name']  </t>
+          <t xml:space="preserve">//input[@name='user-name']  </t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -1762,7 +1762,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t xml:space="preserve">//input[@name='user-name']  </t>
+          <t xml:space="preserve">//input[@id='user-name' and @name='user-name']  </t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -1774,12 +1774,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>User Name Input</t>
+          <t>User Name (input)</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t xml:space="preserve">//input[@id='user-name' and @name='user-name']  </t>
+          <t xml:space="preserve">//input[@id='user-name']  </t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -1791,7 +1791,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Password Input</t>
+          <t>Password (input)</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -1808,7 +1808,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Login Button</t>
+          <t>Login Button (input)</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -1819,6 +1819,57 @@
       <c r="C82" t="inlineStr">
         <is>
           <t>Sauce_demo_login</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Element: a.btn.gcs-btn.gcs-btn--secondary.gcs-btn--pill.gcs-btn--border.mt-3.mx-1.PLACE AN ALERT  </t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">//a[contains(@class, 'gcs-btn') and contains(text(), 'PLACE AN ALERT')]  </t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Equ_home_page</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>firstNameId</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">//input[@id='firstNameId']  </t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>equ_place_on_alert</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>lastName</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">//input[@id='lastName']  </t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>equ_place_on_alert</t>
         </is>
       </c>
     </row>

--- a/output/xpath_generator/xpath_details.xlsx
+++ b/output/xpath_generator/xpath_details.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C85"/>
+  <dimension ref="A1:C94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1247,12 +1247,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>User Name Input</t>
+          <t>User Name Input Field (id=user-name)</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t xml:space="preserve">//input[@id='user-name']  </t>
+          <t>/input[@id='user-name']</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1264,12 +1264,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>User Name Input Field (id=user-name)</t>
+          <t>User Name Input Field:</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>/input[@id='user-name']</t>
+          <t>//input[@id='user-name']</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1281,29 +1281,29 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>User Name Input Field:</t>
+          <t>User-Name Input Field</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>//input[@id='user-name']</t>
+          <t xml:space="preserve">//input[@id='user-name']  </t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>test</t>
+          <t>sauce_demo_login</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>User-Name Input Field</t>
+          <t>Password Input Field</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t xml:space="preserve">//input[@id='user-name']  </t>
+          <t xml:space="preserve">//input[@id='password']  </t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -1315,12 +1315,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Password Input Field</t>
+          <t>Login Button</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t xml:space="preserve">//input[@id='password']  </t>
+          <t xml:space="preserve">//input[@id='login-button']  </t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -1332,29 +1332,29 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Login Button</t>
+          <t>### Element: Close button</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t xml:space="preserve">//input[@id='login-button']  </t>
+          <t xml:space="preserve">//button[@class='close']  </t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>sauce_demo_login</t>
+          <t>Equfix_place_an_alert</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>### Element: Close button</t>
+          <t>### Element: CONTINUE button</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t xml:space="preserve">//button[@class='close']  </t>
+          <t xml:space="preserve">//button[@id='continue-button']  </t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -1366,12 +1366,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>### Element: CONTINUE button</t>
+          <t>### Element: zip</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t xml:space="preserve">//button[@id='continue-button']  </t>
+          <t xml:space="preserve">//input[@id='zip']  </t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -1383,12 +1383,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>### Element: zip</t>
+          <t>### Element: Select state</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t xml:space="preserve">//input[@id='zip']  </t>
+          <t xml:space="preserve">//button[contains(@text, 'Select state')]  </t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -1400,12 +1400,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>### Element: Select state</t>
+          <t>### Element: city</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t xml:space="preserve">//button[contains(@text, 'Select state')]  </t>
+          <t xml:space="preserve">//input[@id='city']  </t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -1417,12 +1417,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>### Element: city</t>
+          <t>### Element: addressLine2Id</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t xml:space="preserve">//input[@id='city']  </t>
+          <t xml:space="preserve">//input[@id='addressLine2Id']  </t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -1434,12 +1434,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>### Element: addressLine2Id</t>
+          <t>### Element: address</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t xml:space="preserve">//input[@id='addressLine2Id']  </t>
+          <t xml:space="preserve">//input[@id='address']  </t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -1451,12 +1451,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>### Element: address</t>
+          <t>### Element: phoneNumber</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t xml:space="preserve">//input[@id='address']  </t>
+          <t xml:space="preserve">//input[@id='phoneNumber']  </t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -1468,12 +1468,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>### Element: phoneNumber</t>
+          <t>### Element: ssn</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t xml:space="preserve">//input[@id='phoneNumber']  </t>
+          <t xml:space="preserve">//input[@id='ssn']  </t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -1485,12 +1485,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>### Element: ssn</t>
+          <t>### Element: dob</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t xml:space="preserve">//input[@id='ssn']  </t>
+          <t xml:space="preserve">//input[@id='dob']  </t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -1502,12 +1502,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>### Element: dob</t>
+          <t>### Element: lastName</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t xml:space="preserve">//input[@id='dob']  </t>
+          <t xml:space="preserve">//input[@id='lastName']  </t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -1519,12 +1519,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>### Element: lastName</t>
+          <t>### Element: firstNameId</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t xml:space="preserve">//input[@id='lastName']  </t>
+          <t xml:space="preserve">//input[@id='firstNameId']  </t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -1536,7 +1536,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>### Element: firstNameId</t>
+          <t>### firstNameId</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -1546,19 +1546,19 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Equfix_place_an_alert</t>
+          <t>Equfixplaceanalert</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>### firstNameId</t>
+          <t>### lastName</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t xml:space="preserve">//input[@id='firstNameId']  </t>
+          <t xml:space="preserve">//input[@id='lastName']  </t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -1570,12 +1570,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>### lastName</t>
+          <t>### dob</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t xml:space="preserve">//input[@id='lastName']  </t>
+          <t xml:space="preserve">//input[@id='dob']  </t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -1587,12 +1587,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>### dob</t>
+          <t>### ssn</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t xml:space="preserve">//input[@id='dob']  </t>
+          <t xml:space="preserve">//input[@id='ssn']  </t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -1604,12 +1604,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>### ssn</t>
+          <t>### phoneNumber</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t xml:space="preserve">//input[@id='ssn']  </t>
+          <t xml:space="preserve">//input[@id='phoneNumber']  </t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -1621,12 +1621,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>### phoneNumber</t>
+          <t>### address</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t xml:space="preserve">//input[@id='phoneNumber']  </t>
+          <t xml:space="preserve">//input[@id='address']  </t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -1638,12 +1638,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>### address</t>
+          <t>### addressLine2Id</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t xml:space="preserve">//input[@id='address']  </t>
+          <t xml:space="preserve">//input[@id='addressLine2Id']  </t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -1655,12 +1655,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>### addressLine2Id</t>
+          <t>### city</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t xml:space="preserve">//input[@id='addressLine2Id']  </t>
+          <t xml:space="preserve">//input[@id='city']  </t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -1672,12 +1672,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>### city</t>
+          <t>### zip</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t xml:space="preserve">//input[@id='city']  </t>
+          <t xml:space="preserve">//input[@id='zip']  </t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -1689,12 +1689,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>### zip</t>
+          <t>### efx-dropdown-label-796908</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t xml:space="preserve">//input[@id='zip']  </t>
+          <t xml:space="preserve">//button[starts-with(@id, 'efx-dropdown-label')]  </t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -1706,12 +1706,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>### efx-dropdown-label-796908</t>
+          <t>### continue-button</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t xml:space="preserve">//button[starts-with(@id, 'efx-dropdown-label')]  </t>
+          <t xml:space="preserve">//button[@id='continue-button']  </t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -1723,17 +1723,17 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>### continue-button</t>
+          <t>User Name Input</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t xml:space="preserve">//button[@id='continue-button']  </t>
+          <t xml:space="preserve">//input[@name='user-name']  </t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Equfixplaceanalert</t>
+          <t>Sauce_demo_login</t>
         </is>
       </c>
     </row>
@@ -1745,7 +1745,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t xml:space="preserve">//input[@name='user-name']  </t>
+          <t xml:space="preserve">//input[@id='user-name' and @name='user-name']  </t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -1757,12 +1757,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>User Name Input</t>
+          <t>User Name (input)</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t xml:space="preserve">//input[@id='user-name' and @name='user-name']  </t>
+          <t xml:space="preserve">//input[@id='user-name']  </t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -1774,12 +1774,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>User Name (input)</t>
+          <t>Password (input)</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t xml:space="preserve">//input[@id='user-name']  </t>
+          <t xml:space="preserve">//input[@id='password']  </t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -1791,12 +1791,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Password (input)</t>
+          <t>Login Button (input)</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t xml:space="preserve">//input[@id='password']  </t>
+          <t xml:space="preserve">//input[@id='login-button']  </t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -1808,46 +1808,46 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Login Button (input)</t>
+          <t xml:space="preserve">Element: a.btn.gcs-btn.gcs-btn--secondary.gcs-btn--pill.gcs-btn--border.mt-3.mx-1.PLACE AN ALERT  </t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t xml:space="preserve">//input[@id='login-button']  </t>
+          <t xml:space="preserve">//a[contains(@class, 'gcs-btn') and contains(text(), 'PLACE AN ALERT')]  </t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Sauce_demo_login</t>
+          <t>Equ_home_page</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t xml:space="preserve">Element: a.btn.gcs-btn.gcs-btn--secondary.gcs-btn--pill.gcs-btn--border.mt-3.mx-1.PLACE AN ALERT  </t>
+          <t>firstNameId</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t xml:space="preserve">//a[contains(@class, 'gcs-btn') and contains(text(), 'PLACE AN ALERT')]  </t>
+          <t xml:space="preserve">//input[@id='firstNameId']  </t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Equ_home_page</t>
+          <t>equ_place_on_alert</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>firstNameId</t>
+          <t>lastName</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t xml:space="preserve">//input[@id='firstNameId']  </t>
+          <t xml:space="preserve">//input[@id='lastName']  </t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -1859,17 +1859,170 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
+          <t>firstNameId</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>//input[@id='firstNameId']</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>equfix_palce_alert</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
           <t>lastName</t>
         </is>
       </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t xml:space="preserve">//input[@id='lastName']  </t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>equ_place_on_alert</t>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>//input[@id='lastName']</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>equfix_palce_alert</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>User-Name Input</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">//form//input[@id='user-name']  </t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>test_login</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Password Input</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t xml:space="preserve">//input[@id='password']  </t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>test_login</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Login-Button Input</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">//input[@id='login-button']  </t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>test_login</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>User Name</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t xml:space="preserve">//*[@id='user-name']  </t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>test_xpath</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">User Name Input  </t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">//input[@name='user-name']  </t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>test_xpath</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Password Input  </t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t xml:space="preserve">//input[@name='password']  </t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>test_xpath</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Login Button Input  </t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t xml:space="preserve">//input[@id='login-button']  </t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>test_xpath</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>User Name Field</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">//input[@id='user-name']  </t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>test</t>
         </is>
       </c>
     </row>

--- a/output/xpath_generator/xpath_details.xlsx
+++ b/output/xpath_generator/xpath_details.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C94"/>
+  <dimension ref="A1:C107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2026,6 +2026,227 @@
         </is>
       </c>
     </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>lastName</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>//input[@id='lastName']</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>equ_place_an_alert</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>dob</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>//input[@id='dob']</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>equ_place_an_alert</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>close</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>//button[@class='close']</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>equ_place_an_alert</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>continue-button</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>//button[@id='continue-button']</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>equ_place_an_alert</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>zip</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>//input[@id='zip']</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>equ_place_an_alert</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>firstNameId</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>//input[@id='firstNameId']</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>equ_place</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>lastName</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>//input[@id='lastName']</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>equ_place</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>dob</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>//input[@id='dob']</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>equ_place</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>User Name Field</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t xml:space="preserve">//input[@id='user-name']  </t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>sauce_demo_new_login</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Password Field  </t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t xml:space="preserve">//input[@id='password']  </t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>sauce_demo_new_login</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Login Button  </t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t xml:space="preserve">//input[@id='login-button']  </t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>sauce_demo_new_login</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t xml:space="preserve">User Name  </t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t xml:space="preserve">//form//input[@id='user-name']  </t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>User Name (id: user-name)</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>/input[@name='user-name' and contains(@class, 'form_input')]</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/xpath_generator/xpath_details.xlsx
+++ b/output/xpath_generator/xpath_details.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C107"/>
+  <dimension ref="A1:C133"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2247,6 +2247,448 @@
         </is>
       </c>
     </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Search Button</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>//li//i[@class='fas fa-search']</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Mckesson_Home</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Search Box</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>//input[contains(@placeholder,'What can we help you find?')]</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Mckesson_Home</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Search submit</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>//span[@class='fas fa-search']</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Mckesson_Home</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Gloves</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>//a[contains(text(),'Gloves')]</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Mckesson_Home</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>a with text="Compression Gloves (99)"</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>//a[contains(text(), 'Compression Gloves')]</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Mckesson_product</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Impact Gloves  </t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t xml:space="preserve">//a[contains(text(), 'Impact Gloves')]  </t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Mckesson_product</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>a with text="Finger Cots (17)"</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>//a[contains(text(), 'Finger Cots')]</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Mckesson_product</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>second prodouct to compare</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>(//a[contains(@class, 'compare-btn')])[1]</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Mckesson_compare</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>compare two producta</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>//a[contains(text(),'Compare Products')]</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Mckesson_compare</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Gloves</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>//a[text()='Gloves']</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Mckesson_home_1</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t xml:space="preserve">a[text()='Compression Gloves (99)']  </t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t xml:space="preserve">//a[text()='Compression Gloves (99)']  </t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>mckesson_gloves</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t xml:space="preserve">a[text()='Exam Gloves (828)']  </t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t xml:space="preserve">//a[text()='Exam Gloves (828)']  </t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>mckesson_gloves</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t xml:space="preserve">a[text()='Finger Cots (17)']  </t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t xml:space="preserve">//a[text()='Finger Cots (17)']  </t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>mckesson_gloves</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Glove Liners (57)  </t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t xml:space="preserve">//a[text()='Glove Liners (57)']  </t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>mckesson_gloves</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t xml:space="preserve">White (56)  </t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>//a[text()='Beige (1)']</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>mckesson_Glove_Liners</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>For "a" with id="a-tab-allproducts", class="catalog-context tab-click ", and text="All Products (57)":</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>//a[text()='All Products (57)']</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>mckesson_Glove_Liners</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>For "a" with id="a-tab-allproducts", class="catalog-context tab-click ", and text="All Products (99)":</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>//a[text()='All Products (99)']</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>mckesson_compression_gloves</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>For "a" with id="a-tab-allproducts", class="catalog-context tab-click ", and text="All Products (828)":</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>//a[text()='All Products (828)']</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>mckesson_exam_gloves</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>For "a" with id="a-tab-allproducts", class="catalog-context tab-click ", and text="All Products (17)":</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>//a[text()='All Products (17)']</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>mckesson_finger_cots</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Button with class "btn btn-default"  </t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t xml:space="preserve">//button[@class='btn btn-default']  </t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>User Name Input Field</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t xml:space="preserve">//input[@id='user-name']  </t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>sauce_demo_login_page</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Password Input Field</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t xml:space="preserve">//input[@id='password']  </t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>sauce_demo_login_page</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Login Button</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t xml:space="preserve">//input[@id='login-button']  </t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>sauce_demo_login_page</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>User Name</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t xml:space="preserve">//input[@id='user-name']  </t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>jan_sauce_demo_login</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Password  </t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t xml:space="preserve">//input[@id='password']  </t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>jan_sauce_demo_login</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Login Button  </t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t xml:space="preserve">//input[@id='login-button']  </t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>jan_sauce_demo_login</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/xpath_generator/xpath_details.xlsx
+++ b/output/xpath_generator/xpath_details.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C133"/>
+  <dimension ref="A1:C149"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2689,6 +2689,278 @@
         </is>
       </c>
     </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>FirstName</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>//input[@id="FirstName"]</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>mckesson_form</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>LastName</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>//input[@id="LastName"]</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>mckesson_form</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>//input[@id="Email"]</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>mckesson_form</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>//input[@id="Company"]</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>mckesson_form</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>mKTOWebsite</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>//input[@id="mKTOWebsite"]</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>mckesson_form</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>//input[@id="Phone"]</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>mckesson_form</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>//input[@id="Title"]</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>mckesson_form</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>City</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>//input[@id="City"]</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>mckesson_form</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>State</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>//select[@id="State"]</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>mckesson_form</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t xml:space="preserve">**mktoCheckbox_23066_0**  </t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t xml:space="preserve">//input[@id='mktoCheckbox_23066_0']  </t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>mckesson_form</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t xml:space="preserve">**mktoCheckbox_23066_1**  </t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t xml:space="preserve">//input[@id='mktoCheckbox_23066_1']  </t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>mckesson_form</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t xml:space="preserve">**mktoCheckbox_23066_2**  </t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t xml:space="preserve">//input[@id='mktoCheckbox_23066_2']  </t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>mckesson_form</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t xml:space="preserve">**mktoCheckbox_23066_3**  </t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t xml:space="preserve">//input[@id='mktoCheckbox_23066_3']  </t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>mckesson_form</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t xml:space="preserve">**mktoRadio_23069_0**  </t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t xml:space="preserve">//input[@id='mktoRadio_23069_0']  </t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>mckesson_form</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t xml:space="preserve">**Primary_Customer_Number__c**  </t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t xml:space="preserve">//input[@id='Primary_Customer_Number__c']  </t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>mckesson_form</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t xml:space="preserve">**Submit Button**  </t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t xml:space="preserve">//button[@type='submit']  </t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>mckesson_form</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/xpath_generator/xpath_details.xlsx
+++ b/output/xpath_generator/xpath_details.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C149"/>
+  <dimension ref="A1:C171"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2012,29 +2012,29 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>User Name Field</t>
+          <t>lastName</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t xml:space="preserve">//input[@id='user-name']  </t>
+          <t>//input[@id='lastName']</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>test</t>
+          <t>equ_place_an_alert</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>lastName</t>
+          <t>dob</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>//input[@id='lastName']</t>
+          <t>//input[@id='dob']</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -2046,12 +2046,12 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>dob</t>
+          <t>close</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>//input[@id='dob']</t>
+          <t>//button[@class='close']</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -2063,12 +2063,12 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>close</t>
+          <t>continue-button</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>//button[@class='close']</t>
+          <t>//button[@id='continue-button']</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -2080,12 +2080,12 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>continue-button</t>
+          <t>zip</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>//button[@id='continue-button']</t>
+          <t>//input[@id='zip']</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -2097,29 +2097,29 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>zip</t>
+          <t>firstNameId</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>//input[@id='zip']</t>
+          <t>//input[@id='firstNameId']</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>equ_place_an_alert</t>
+          <t>equ_place</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>firstNameId</t>
+          <t>lastName</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>//input[@id='firstNameId']</t>
+          <t>//input[@id='lastName']</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -2131,12 +2131,12 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>lastName</t>
+          <t>dob</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>//input[@id='lastName']</t>
+          <t>//input[@id='dob']</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -2148,29 +2148,29 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>dob</t>
+          <t>User Name Field</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>//input[@id='dob']</t>
+          <t xml:space="preserve">//input[@id='user-name']  </t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>equ_place</t>
+          <t>sauce_demo_new_login</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>User Name Field</t>
+          <t xml:space="preserve">Password Field  </t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t xml:space="preserve">//input[@id='user-name']  </t>
+          <t xml:space="preserve">//input[@id='password']  </t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -2182,12 +2182,12 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t xml:space="preserve">Password Field  </t>
+          <t xml:space="preserve">Login Button  </t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t xml:space="preserve">//input[@id='password']  </t>
+          <t xml:space="preserve">//input[@id='login-button']  </t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -2199,29 +2199,29 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t xml:space="preserve">Login Button  </t>
+          <t xml:space="preserve">User Name  </t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t xml:space="preserve">//input[@id='login-button']  </t>
+          <t xml:space="preserve">//form//input[@id='user-name']  </t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>sauce_demo_new_login</t>
+          <t>new</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t xml:space="preserve">User Name  </t>
+          <t>User Name (id: user-name)</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t xml:space="preserve">//form//input[@id='user-name']  </t>
+          <t>/input[@name='user-name' and contains(@class, 'form_input')]</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -2233,29 +2233,29 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>User Name (id: user-name)</t>
+          <t>Search Button</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>/input[@name='user-name' and contains(@class, 'form_input')]</t>
+          <t>//li//i[@class='fas fa-search']</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>new</t>
+          <t>Mckesson_Home</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Search Button</t>
+          <t>Search Box</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>//li//i[@class='fas fa-search']</t>
+          <t>//input[contains(@placeholder,'What can we help you find?')]</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -2267,12 +2267,12 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Search Box</t>
+          <t>Search submit</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>//input[contains(@placeholder,'What can we help you find?')]</t>
+          <t>//span[@class='fas fa-search']</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -2284,12 +2284,12 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Search submit</t>
+          <t>Gloves</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>//span[@class='fas fa-search']</t>
+          <t>//a[contains(text(),'Gloves')]</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -2301,29 +2301,29 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Gloves</t>
+          <t>a with text="Compression Gloves (99)"</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>//a[contains(text(),'Gloves')]</t>
+          <t>//a[contains(text(), 'Compression Gloves')]</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Mckesson_Home</t>
+          <t>Mckesson_product</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>a with text="Compression Gloves (99)"</t>
+          <t xml:space="preserve">Impact Gloves  </t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>//a[contains(text(), 'Compression Gloves')]</t>
+          <t xml:space="preserve">//a[contains(text(), 'Impact Gloves')]  </t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -2335,12 +2335,12 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t xml:space="preserve">Impact Gloves  </t>
+          <t>a with text="Finger Cots (17)"</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t xml:space="preserve">//a[contains(text(), 'Impact Gloves')]  </t>
+          <t>//a[contains(text(), 'Finger Cots')]</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -2352,29 +2352,29 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>a with text="Finger Cots (17)"</t>
+          <t>second prodouct to compare</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>//a[contains(text(), 'Finger Cots')]</t>
+          <t>(//a[contains(@class, 'compare-btn')])[1]</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Mckesson_product</t>
+          <t>Mckesson_compare</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>second prodouct to compare</t>
+          <t>compare two producta</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>(//a[contains(@class, 'compare-btn')])[1]</t>
+          <t>//a[contains(text(),'Compare Products')]</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -2386,46 +2386,46 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>compare two producta</t>
+          <t>Gloves</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>//a[contains(text(),'Compare Products')]</t>
+          <t>//a[text()='Gloves']</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Mckesson_compare</t>
+          <t>Mckesson_home_1</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Gloves</t>
+          <t xml:space="preserve">a[text()='Compression Gloves (99)']  </t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>//a[text()='Gloves']</t>
+          <t xml:space="preserve">//a[text()='Compression Gloves (99)']  </t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Mckesson_home_1</t>
+          <t>mckesson_gloves</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t xml:space="preserve">a[text()='Compression Gloves (99)']  </t>
+          <t xml:space="preserve">a[text()='Exam Gloves (828)']  </t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t xml:space="preserve">//a[text()='Compression Gloves (99)']  </t>
+          <t xml:space="preserve">//a[text()='Exam Gloves (828)']  </t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -2437,12 +2437,12 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t xml:space="preserve">a[text()='Exam Gloves (828)']  </t>
+          <t xml:space="preserve">a[text()='Finger Cots (17)']  </t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t xml:space="preserve">//a[text()='Exam Gloves (828)']  </t>
+          <t xml:space="preserve">//a[text()='Finger Cots (17)']  </t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -2454,12 +2454,12 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t xml:space="preserve">a[text()='Finger Cots (17)']  </t>
+          <t xml:space="preserve">Glove Liners (57)  </t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t xml:space="preserve">//a[text()='Finger Cots (17)']  </t>
+          <t xml:space="preserve">//a[text()='Glove Liners (57)']  </t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -2471,29 +2471,29 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t xml:space="preserve">Glove Liners (57)  </t>
+          <t xml:space="preserve">White (56)  </t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t xml:space="preserve">//a[text()='Glove Liners (57)']  </t>
+          <t>//a[text()='Beige (1)']</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>mckesson_gloves</t>
+          <t>mckesson_Glove_Liners</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t xml:space="preserve">White (56)  </t>
+          <t>For "a" with id="a-tab-allproducts", class="catalog-context tab-click ", and text="All Products (57)":</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>//a[text()='Beige (1)']</t>
+          <t>//a[text()='All Products (57)']</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -2505,97 +2505,97 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>For "a" with id="a-tab-allproducts", class="catalog-context tab-click ", and text="All Products (57)":</t>
+          <t>For "a" with id="a-tab-allproducts", class="catalog-context tab-click ", and text="All Products (99)":</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>//a[text()='All Products (57)']</t>
+          <t>//a[text()='All Products (99)']</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>mckesson_Glove_Liners</t>
+          <t>mckesson_compression_gloves</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>For "a" with id="a-tab-allproducts", class="catalog-context tab-click ", and text="All Products (99)":</t>
+          <t>For "a" with id="a-tab-allproducts", class="catalog-context tab-click ", and text="All Products (828)":</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>//a[text()='All Products (99)']</t>
+          <t>//a[text()='All Products (828)']</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>mckesson_compression_gloves</t>
+          <t>mckesson_exam_gloves</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>For "a" with id="a-tab-allproducts", class="catalog-context tab-click ", and text="All Products (828)":</t>
+          <t>For "a" with id="a-tab-allproducts", class="catalog-context tab-click ", and text="All Products (17)":</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>//a[text()='All Products (828)']</t>
+          <t>//a[text()='All Products (17)']</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>mckesson_exam_gloves</t>
+          <t>mckesson_finger_cots</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>For "a" with id="a-tab-allproducts", class="catalog-context tab-click ", and text="All Products (17)":</t>
+          <t xml:space="preserve">Button with class "btn btn-default"  </t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>//a[text()='All Products (17)']</t>
+          <t xml:space="preserve">//button[@class='btn btn-default']  </t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>mckesson_finger_cots</t>
+          <t>test</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t xml:space="preserve">Button with class "btn btn-default"  </t>
+          <t>User Name Input Field</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t xml:space="preserve">//button[@class='btn btn-default']  </t>
+          <t xml:space="preserve">//input[@id='user-name']  </t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>test</t>
+          <t>sauce_demo_login_page</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>User Name Input Field</t>
+          <t>Password Input Field</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t xml:space="preserve">//input[@id='user-name']  </t>
+          <t xml:space="preserve">//input[@id='password']  </t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -2607,12 +2607,12 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Password Input Field</t>
+          <t>Login Button</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t xml:space="preserve">//input[@id='password']  </t>
+          <t xml:space="preserve">//input[@id='login-button']  </t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -2624,29 +2624,29 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Login Button</t>
+          <t>User Name</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t xml:space="preserve">//input[@id='login-button']  </t>
+          <t xml:space="preserve">//input[@id='user-name']  </t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>sauce_demo_login_page</t>
+          <t>jan_sauce_demo_login</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>User Name</t>
+          <t xml:space="preserve">Password  </t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t xml:space="preserve">//input[@id='user-name']  </t>
+          <t xml:space="preserve">//input[@id='password']  </t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -2658,12 +2658,12 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t xml:space="preserve">Password  </t>
+          <t xml:space="preserve">Login Button  </t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t xml:space="preserve">//input[@id='password']  </t>
+          <t xml:space="preserve">//input[@id='login-button']  </t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -2675,29 +2675,29 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t xml:space="preserve">Login Button  </t>
+          <t>FirstName</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t xml:space="preserve">//input[@id='login-button']  </t>
+          <t>//input[@id="FirstName"]</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>jan_sauce_demo_login</t>
+          <t>mckesson_form</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>FirstName</t>
+          <t>LastName</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>//input[@id="FirstName"]</t>
+          <t>//input[@id="LastName"]</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -2709,12 +2709,12 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>LastName</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>//input[@id="LastName"]</t>
+          <t>//input[@id="Email"]</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -2726,12 +2726,12 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Company</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>//input[@id="Email"]</t>
+          <t>//input[@id="Company"]</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -2743,12 +2743,12 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Company</t>
+          <t>mKTOWebsite</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>//input[@id="Company"]</t>
+          <t>//input[@id="mKTOWebsite"]</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -2760,12 +2760,12 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>mKTOWebsite</t>
+          <t>Phone</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>//input[@id="mKTOWebsite"]</t>
+          <t>//input[@id="Phone"]</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -2777,12 +2777,12 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Phone</t>
+          <t>Title</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>//input[@id="Phone"]</t>
+          <t>//input[@id="Title"]</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -2794,12 +2794,12 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Title</t>
+          <t>City</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>//input[@id="Title"]</t>
+          <t>//input[@id="City"]</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -2811,12 +2811,12 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>City</t>
+          <t>State</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>//input[@id="City"]</t>
+          <t>//select[@id="State"]</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -2828,12 +2828,12 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>State</t>
+          <t xml:space="preserve">**mktoCheckbox_23066_0**  </t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>//select[@id="State"]</t>
+          <t xml:space="preserve">//input[@id='mktoCheckbox_23066_0']  </t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -2845,12 +2845,12 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t xml:space="preserve">**mktoCheckbox_23066_0**  </t>
+          <t xml:space="preserve">**mktoCheckbox_23066_1**  </t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t xml:space="preserve">//input[@id='mktoCheckbox_23066_0']  </t>
+          <t xml:space="preserve">//input[@id='mktoCheckbox_23066_1']  </t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -2862,12 +2862,12 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t xml:space="preserve">**mktoCheckbox_23066_1**  </t>
+          <t xml:space="preserve">**mktoCheckbox_23066_2**  </t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t xml:space="preserve">//input[@id='mktoCheckbox_23066_1']  </t>
+          <t xml:space="preserve">//input[@id='mktoCheckbox_23066_2']  </t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -2879,12 +2879,12 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t xml:space="preserve">**mktoCheckbox_23066_2**  </t>
+          <t xml:space="preserve">**mktoCheckbox_23066_3**  </t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t xml:space="preserve">//input[@id='mktoCheckbox_23066_2']  </t>
+          <t xml:space="preserve">//input[@id='mktoCheckbox_23066_3']  </t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -2896,12 +2896,12 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t xml:space="preserve">**mktoCheckbox_23066_3**  </t>
+          <t xml:space="preserve">**mktoRadio_23069_0**  </t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t xml:space="preserve">//input[@id='mktoCheckbox_23066_3']  </t>
+          <t xml:space="preserve">//input[@id='mktoRadio_23069_0']  </t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -2913,12 +2913,12 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t xml:space="preserve">**mktoRadio_23069_0**  </t>
+          <t xml:space="preserve">**Primary_Customer_Number__c**  </t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t xml:space="preserve">//input[@id='mktoRadio_23069_0']  </t>
+          <t xml:space="preserve">//input[@id='Primary_Customer_Number__c']  </t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -2930,12 +2930,12 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t xml:space="preserve">**Primary_Customer_Number__c**  </t>
+          <t xml:space="preserve">**Submit Button**  </t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t xml:space="preserve">//input[@id='Primary_Customer_Number__c']  </t>
+          <t xml:space="preserve">//button[@type='submit']  </t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -2947,17 +2947,391 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t xml:space="preserve">**Submit Button**  </t>
+          <t>User Name Input</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t xml:space="preserve">//button[@type='submit']  </t>
+          <t xml:space="preserve">//input[@id='user-name']  </t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>mckesson_form</t>
+          <t>test</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>Continue Button</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>//*[text()='Continue']</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>add</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t xml:space="preserve">First Name Field  </t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t xml:space="preserve">//input[@id='firstNameId']  </t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>equi_place_on_alert</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Last Name Field  </t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t xml:space="preserve">//input[@id='lastName']  </t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>equi_place_on_alert</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Date of Birth Field  </t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t xml:space="preserve">//input[@id='dob']  </t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>equi_place_on_alert</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SSN Field  </t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t xml:space="preserve">//input[@id='ssn']  </t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>equi_place_on_alert</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Phone Number Field  </t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t xml:space="preserve">//input[@id='phoneNumber']  </t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>equi_place_on_alert</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Address Line 1 Field  </t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t xml:space="preserve">//input[@id='address']  </t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>equi_place_on_alert</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Address Line 2 Field  </t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t xml:space="preserve">//input[@id='addressLine2Id']  </t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>equi_place_on_alert</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t xml:space="preserve">City Field  </t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t xml:space="preserve">//input[@id='city']  </t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>equi_place_on_alert</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>No parent-child hierarchical relationships were detected in this input structure. All elements are presented as standalone. No nested hierarchy-based XPaths generated.</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t xml:space="preserve">//input[@id='username']  </t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>Sfdc_login</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>### Password Input Field</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t xml:space="preserve">//input[@id='password']  </t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>Sfdc_login</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>### Login Button</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t xml:space="preserve">//input[@id='Login']  </t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>Sfdc_login</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>Input Field (id: emc)</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>//input[@type='text']</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>sfdc_otp</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>Save Button (id: save)</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>//input[@type='submit']</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>sfdc_otp</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t># "Contacts"</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t xml:space="preserve">//span[text()='Contacts']  </t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>sfdc_homepage</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t># "Contacts"</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>//button[contains(text(),'New')]</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>sfdc_contact_new</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t># "Contacts"</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>//input[@name='lastName']</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>sfdc_contact_new</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t xml:space="preserve">**Email Input (id="input-795")**  </t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t xml:space="preserve">//input[@name='Email']  </t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>sfdc_contact_new</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>**Assistant Name Input (id="input-808")**</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t xml:space="preserve">//input[@name='AssistantName']  </t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>sfdc_contact_new</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>**Bio Input (id="input-813")**</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t xml:space="preserve">//input[@name='Bio__c']  </t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>sfdc_contact_new</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>**Assistant Phone Input (id="input-816")**</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t xml:space="preserve">//input[@name='AssistantPhone']  </t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>sfdc_contact_new</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>### Save Button</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t xml:space="preserve">`//button[@name='SaveEdit']`  </t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>sfdc_contact_new</t>
         </is>
       </c>
     </row>

--- a/output/xpath_generator/xpath_details.xlsx
+++ b/output/xpath_generator/xpath_details.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C171"/>
+  <dimension ref="A1:C202"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3335,6 +3335,533 @@
         </is>
       </c>
     </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>user-name (id='user-name')</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>//*[@id='user-name']</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>mar_19_suce</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>password (id='password')</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>//input[@id='password']</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>mar_19_suce</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>login-button (id='login-button')</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>//*[@id='login-button']</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>mar_19_suce</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>Input - id='user-name' name='user-name'</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>//input[@id='user-name']</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>mar_sauce_demo_login</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>Input - id='password' name='password'</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>//input[@id='password']</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>mar_sauce_demo_login</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>Input (submit) - id='login-button' name='login-button'</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>//input[@id='login-button']</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>mar_sauce_demo_login</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>login-button (id='login-button', name='login-button', type='submit')</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> //input[@id='login-button']</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>new_page_file_sauce_demo</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>password (id='password', name='password')</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> //input[@id='password']</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>new_page_file_sauce_demo</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>user-name (id='user-name', name='user-name')</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> //input[@id='user-name']</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>new_page_file_sauce_demo</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>Open Menu (react-burger-menu-btn)</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> //button[@id='react-burger-menu-btn']</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>inventory_sauce_demo</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>Shopping Cart Link (shopping_cart_link)</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> //a[@class='shopping_cart_link']</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>inventory_sauce_demo</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>Sauce Labs Backpack (item_4)</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> //button[@id='add-to-cart-sauce-labs-backpack']</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>inventory_sauce_demo</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>Sauce Labs Bike Light (item_0)</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> //button[@id='add-to-cart-sauce-labs-bike-light']</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>inventory_sauce_demo</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>Sauce Labs Bolt T-Shirt (item_1)</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> //button[@id='add-to-cart-sauce-labs-bolt-t-shirt']</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>inventory_sauce_demo</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>Sauce Labs Fleece Jacket (item_5)</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> //button[@id='add-to-cart-sauce-labs-fleece-jacket']</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>inventory_sauce_demo</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>Add to cart (add-to-cart-sauce-labs-onesie)</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> //button[@name='add-to-cart-sauce-labs-onesie']</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>inventory_sauce_demo</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>Add to cart (add-to-cart-test.allthethings()-t-shirt-(red))</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> //button[@id='add-to-cart-test.allthethings()-t-shirt-(red)']</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>inventory_sauce_demo</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>Remove (Backpack) (id=remove-sauce-labs-backpack)</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> //button[@id='remove-sauce-labs-backpack']</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>cart_sauce_demo</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>Remove (Bike Light) (id=remove-sauce-labs-bike-light)</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> //button[@id='remove-sauce-labs-bike-light']</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>cart_sauce_demo</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>Continue Shopping (id=continue-shopping)</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> //button[@id='continue-shopping']</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>cart_sauce_demo</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>Checkout (id=checkout)</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> //button[@id='checkout']</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>cart_sauce_demo</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>First Name (input#first-name | name=firstName)</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> //input[@id='first-name']</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>checkout_step_one</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>Last Name (input#last-name | name=lastName)</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> //input[@id='last-name']</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>checkout_step_one</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>Postal Code (input#postal-code | name=postalCode)</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> //input[@id='postal-code']</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>checkout_step_one</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>Cancel (button#cancel | name=cancel | text=Cancel)</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> //button[@id='cancel']</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>checkout_step_one</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>Continue (input#continue | name=continue | type=submit)</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> //input[@id='continue']</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>checkout_step_one</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>Cancel (id=cancel, name=cancel)</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> //button[@id='cancel']</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>checkout_step_two</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>Finish (id=finish, name=finish)</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> //button[@id='finish']</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>checkout_step_two</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>Back Home (id=back-to-products)</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> //button[@id='back-to-products']</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>checkout_complete</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>Logout (id=logout_sidebar_link)</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> //a[@id='logout_sidebar_link']</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>home_logout_sauce_demo</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>Reset App State (id=reset_sidebar_link)</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> //a[@id='reset_sidebar_link']</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>home_logout_sauce_demo</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/xpath_generator/xpath_details.xlsx
+++ b/output/xpath_generator/xpath_details.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C202"/>
+  <dimension ref="A1:C208"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3862,6 +3862,108 @@
         </is>
       </c>
     </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>Username input (id='username', name='username')</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> //input[@id='username']</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>sfdc_login</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>Password input (id='password', name='pw')</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> //input[@id='password']</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>sfdc_login</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>Login button (id='Login', name='Login')</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> //input[@id='Login']</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>sfdc_login</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>user-name (input id='user-name')</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> //input[@id='user-name']</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>ap_sauce</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>password (input id='password')</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> //input[@id='password']</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>ap_sauce</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>login-button (input id='login-button')</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> //input[@id='login-button']</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>ap_sauce</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/xpath_generator/xpath_details.xlsx
+++ b/output/xpath_generator/xpath_details.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C208"/>
+  <dimension ref="A1:C211"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3964,6 +3964,57 @@
         </is>
       </c>
     </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>Input (id='user-name')</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> //input[@id='user-name']</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>test_xapth</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>Input (id='password')</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> //input[@id='password']</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>test_xapth</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>user-name (id='user-name')</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> //input[@id='user-name']</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>login_page</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/xpath_generator/xpath_details.xlsx
+++ b/output/xpath_generator/xpath_details.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C211"/>
+  <dimension ref="A1:C214"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4015,6 +4015,57 @@
         </is>
       </c>
     </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>user-name (input id='user-name')</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> //input[@id='user-name']</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>sauce_demo_lagin_june</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>password (input id='password')</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> //input[@id='password']</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>sauce_demo_lagin_june</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>login-button (input id='login-button')</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> //input[@id='login-button']</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>sauce_demo_lagin_june</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/xpath_generator/xpath_details.xlsx
+++ b/output/xpath_generator/xpath_details.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C214"/>
+  <dimension ref="A1:C216"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4066,6 +4066,40 @@
         </is>
       </c>
     </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>Input @id='user-name'</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>//input[@id='user-name']</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>sauce_logi</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>Hierarchical combined XPaths</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>//input[@id='login-button']/preceding-sibling::input[@id='password']</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>sauce_logi</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/xpath_generator/xpath_details.xlsx
+++ b/output/xpath_generator/xpath_details.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C216"/>
+  <dimension ref="A1:C218"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4100,6 +4100,40 @@
         </is>
       </c>
     </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>user-name (id='user-name')</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> //input[@id='login-button']</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>test_login</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>user-name (id='user-name')</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> //input[@id='password']/preceding::input[@id='user-name']</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>test_login</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
